--- a/stacked_model/results/ablation/ablation_top_candidates.xlsx
+++ b/stacked_model/results/ablation/ablation_top_candidates.xlsx
@@ -507,19 +507,19 @@
         <v>959.2222212006562</v>
       </c>
       <c r="G2" t="n">
-        <v>3.054853077716411</v>
+        <v>3.054853077716398</v>
       </c>
       <c r="H2" t="n">
         <v>4.911296439845443</v>
       </c>
       <c r="I2" t="n">
-        <v>90.6398084036133</v>
+        <v>90.63981244359209</v>
       </c>
       <c r="J2" t="n">
-        <v>6.124067204543739</v>
+        <v>5.958147515790889</v>
       </c>
       <c r="K2" t="n">
-        <v>0.908635064160345</v>
+        <v>0.9066673444051729</v>
       </c>
     </row>
     <row r="3">
@@ -544,19 +544,19 @@
         <v>934.4784837879893</v>
       </c>
       <c r="G3" t="n">
-        <v>2.796265769646185</v>
+        <v>2.796265769646167</v>
       </c>
       <c r="H3" t="n">
-        <v>5.842139841967368</v>
+        <v>5.842139841967365</v>
       </c>
       <c r="I3" t="n">
-        <v>89.75866628974364</v>
+        <v>89.75865251071539</v>
       </c>
       <c r="J3" t="n">
-        <v>7.659917675053562</v>
+        <v>7.527948010341123</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9030901873333845</v>
+        <v>0.9023953084964481</v>
       </c>
     </row>
     <row r="4">
@@ -581,19 +581,19 @@
         <v>929.8717425622768</v>
       </c>
       <c r="G4" t="n">
-        <v>2.829558566575855</v>
+        <v>2.829558566575798</v>
       </c>
       <c r="H4" t="n">
-        <v>5.897459292430044</v>
+        <v>5.897459292430039</v>
       </c>
       <c r="I4" t="n">
-        <v>89.76512460309408</v>
+        <v>89.76510962162777</v>
       </c>
       <c r="J4" t="n">
-        <v>7.645550143864765</v>
+        <v>7.513329003516862</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9025576237899711</v>
+        <v>0.9018516087723667</v>
       </c>
     </row>
     <row r="5">
@@ -606,31 +606,31 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.98133423630042</v>
+        <v>-0.9881842858468689</v>
       </c>
       <c r="D5" t="n">
-        <v>1.395349209768287</v>
+        <v>1.197944811492324</v>
       </c>
       <c r="E5" t="n">
-        <v>1.105470462499802</v>
+        <v>1.147634932324883</v>
       </c>
       <c r="F5" t="n">
-        <v>985.0107317824941</v>
+        <v>933.5863365500767</v>
       </c>
       <c r="G5" t="n">
-        <v>3.747264497291497</v>
+        <v>3.206224269650008</v>
       </c>
       <c r="H5" t="n">
-        <v>5.067471482717012</v>
+        <v>5.873811846390021</v>
       </c>
       <c r="I5" t="n">
-        <v>90.39985645846278</v>
+        <v>89.65560004584962</v>
       </c>
       <c r="J5" t="n">
-        <v>6.308978039494022</v>
+        <v>7.585275892952789</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9004522742792861</v>
+        <v>0.898763739787688</v>
       </c>
     </row>
     <row r="6">
@@ -643,31 +643,31 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.9823306052616613</v>
+        <v>-0.98133423630042</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9150562646187159</v>
+        <v>1.395349209768287</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9289872559292436</v>
+        <v>1.105470462499802</v>
       </c>
       <c r="F6" t="n">
-        <v>929.4248881644673</v>
+        <v>985.0107317824941</v>
       </c>
       <c r="G6" t="n">
-        <v>2.699120004101129</v>
+        <v>3.747264497291508</v>
       </c>
       <c r="H6" t="n">
-        <v>4.668149422396129</v>
+        <v>5.067471482717011</v>
       </c>
       <c r="I6" t="n">
-        <v>90.5607541698636</v>
+        <v>90.39985262243552</v>
       </c>
       <c r="J6" t="n">
-        <v>5.922758445777547</v>
+        <v>6.148057097071797</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9001460070614099</v>
+        <v>0.8985832182140933</v>
       </c>
     </row>
     <row r="7">
@@ -680,31 +680,31 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.9881842858468689</v>
+        <v>-0.9823306052616613</v>
       </c>
       <c r="D7" t="n">
-        <v>1.197944811492324</v>
+        <v>0.9150562646187159</v>
       </c>
       <c r="E7" t="n">
-        <v>1.147634932324883</v>
+        <v>0.9289872559292436</v>
       </c>
       <c r="F7" t="n">
-        <v>933.5863365500767</v>
+        <v>929.4248881644673</v>
       </c>
       <c r="G7" t="n">
-        <v>3.20622426965001</v>
+        <v>2.699120004101111</v>
       </c>
       <c r="H7" t="n">
-        <v>5.873811846390026</v>
+        <v>4.668149422396124</v>
       </c>
       <c r="I7" t="n">
-        <v>89.65561914260337</v>
+        <v>90.56077671501814</v>
       </c>
       <c r="J7" t="n">
-        <v>7.716262405861235</v>
+        <v>5.751021662752048</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8994523421227424</v>
+        <v>0.8978608363062656</v>
       </c>
     </row>
     <row r="8">
@@ -717,31 +717,31 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.9779437557508321</v>
+        <v>-0.9753529106293825</v>
       </c>
       <c r="D8" t="n">
-        <v>1.137208374331435</v>
+        <v>1.501908700020724</v>
       </c>
       <c r="E8" t="n">
-        <v>1.034730357262841</v>
+        <v>1.121024007782774</v>
       </c>
       <c r="F8" t="n">
-        <v>931.7453413415755</v>
+        <v>992.2539094228936</v>
       </c>
       <c r="G8" t="n">
-        <v>2.840062785113513</v>
+        <v>3.796557778379044</v>
       </c>
       <c r="H8" t="n">
-        <v>3.747907256253344</v>
+        <v>5.42621810723347</v>
       </c>
       <c r="I8" t="n">
-        <v>91.1673747434628</v>
+        <v>90.06757441015667</v>
       </c>
       <c r="J8" t="n">
-        <v>4.50137399483912</v>
+        <v>6.647340254345798</v>
       </c>
       <c r="K8" t="n">
-        <v>0.897140366848819</v>
+        <v>0.8940480823010662</v>
       </c>
     </row>
     <row r="9">
@@ -754,31 +754,31 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.9753529106293825</v>
+        <v>-0.9779437557508321</v>
       </c>
       <c r="D9" t="n">
-        <v>1.501908700020724</v>
+        <v>1.137208374331435</v>
       </c>
       <c r="E9" t="n">
-        <v>1.121024007782774</v>
+        <v>1.034730357262841</v>
       </c>
       <c r="F9" t="n">
-        <v>992.2539094228936</v>
+        <v>931.7453413415755</v>
       </c>
       <c r="G9" t="n">
-        <v>3.796557778379082</v>
+        <v>2.840062785113556</v>
       </c>
       <c r="H9" t="n">
-        <v>5.426218107233474</v>
+        <v>3.747907256253351</v>
       </c>
       <c r="I9" t="n">
-        <v>90.0675843031344</v>
+        <v>91.16739659197755</v>
       </c>
       <c r="J9" t="n">
-        <v>6.796441376870342</v>
+        <v>4.272865793738961</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8955073396797743</v>
+        <v>0.8929098689845326</v>
       </c>
     </row>
     <row r="10">
@@ -803,19 +803,19 @@
         <v>924.5040419813747</v>
       </c>
       <c r="G10" t="n">
-        <v>3.163171815034923</v>
+        <v>3.163171815034922</v>
       </c>
       <c r="H10" t="n">
-        <v>4.205589412116763</v>
+        <v>4.20558941211676</v>
       </c>
       <c r="I10" t="n">
-        <v>90.89747562682783</v>
+        <v>90.8974872927856</v>
       </c>
       <c r="J10" t="n">
-        <v>5.053048234033386</v>
+        <v>4.850611954098968</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8953006956406104</v>
+        <v>0.8918928272919321</v>
       </c>
     </row>
     <row r="11">
@@ -828,31 +828,31 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.9785128573232006</v>
+        <v>-0.9769674601801612</v>
       </c>
       <c r="D11" t="n">
-        <v>1.406855554262252</v>
+        <v>1.316069276597882</v>
       </c>
       <c r="E11" t="n">
-        <v>1.093271521061723</v>
+        <v>1.135957426920155</v>
       </c>
       <c r="F11" t="n">
-        <v>954.6524202513552</v>
+        <v>876.4872436174745</v>
       </c>
       <c r="G11" t="n">
-        <v>3.595719681393603</v>
+        <v>3.156527371826327</v>
       </c>
       <c r="H11" t="n">
-        <v>4.81113365811927</v>
+        <v>5.702982121395989</v>
       </c>
       <c r="I11" t="n">
-        <v>90.47749704831578</v>
+        <v>89.74993664942699</v>
       </c>
       <c r="J11" t="n">
-        <v>5.868595983977621</v>
+        <v>7.141809198787176</v>
       </c>
       <c r="K11" t="n">
-        <v>0.893030612571645</v>
+        <v>0.8911216145861861</v>
       </c>
     </row>
     <row r="12">
@@ -877,19 +877,19 @@
         <v>934.4784837879893</v>
       </c>
       <c r="G12" t="n">
-        <v>2.796265769646185</v>
+        <v>2.796265769646167</v>
       </c>
       <c r="H12" t="n">
-        <v>5.842139841967368</v>
+        <v>5.842139841967365</v>
       </c>
       <c r="I12" t="n">
-        <v>89.75866628974364</v>
+        <v>89.75865251071539</v>
       </c>
       <c r="J12" t="n">
-        <v>7.659917675053562</v>
+        <v>7.527948010341123</v>
       </c>
       <c r="K12" t="n">
-        <v>0.9748494448968498</v>
+        <v>0.9741545297513206</v>
       </c>
     </row>
     <row r="13">
@@ -914,19 +914,19 @@
         <v>929.8717425622768</v>
       </c>
       <c r="G13" t="n">
-        <v>2.829558566575855</v>
+        <v>2.829558566575798</v>
       </c>
       <c r="H13" t="n">
-        <v>5.897459292430044</v>
+        <v>5.897459292430039</v>
       </c>
       <c r="I13" t="n">
-        <v>89.76512460309408</v>
+        <v>89.76510962162777</v>
       </c>
       <c r="J13" t="n">
-        <v>7.645550143864765</v>
+        <v>7.513329003516862</v>
       </c>
       <c r="K13" t="n">
-        <v>0.9747417514283909</v>
+        <v>0.9740356987963065</v>
       </c>
     </row>
     <row r="14">
@@ -951,19 +951,19 @@
         <v>959.2222212006562</v>
       </c>
       <c r="G14" t="n">
-        <v>3.054853077716411</v>
+        <v>3.054853077716398</v>
       </c>
       <c r="H14" t="n">
         <v>4.911296439845443</v>
       </c>
       <c r="I14" t="n">
-        <v>90.6398084036133</v>
+        <v>90.63981244359209</v>
       </c>
       <c r="J14" t="n">
-        <v>6.124067204543739</v>
+        <v>5.958147515790889</v>
       </c>
       <c r="K14" t="n">
-        <v>0.9743163326573516</v>
+        <v>0.9723485952469719</v>
       </c>
     </row>
     <row r="15">
@@ -988,19 +988,19 @@
         <v>933.5863365500767</v>
       </c>
       <c r="G15" t="n">
-        <v>3.20622426965001</v>
+        <v>3.206224269650008</v>
       </c>
       <c r="H15" t="n">
-        <v>5.873811846390026</v>
+        <v>5.873811846390021</v>
       </c>
       <c r="I15" t="n">
-        <v>89.65561914260337</v>
+        <v>89.65560004584962</v>
       </c>
       <c r="J15" t="n">
-        <v>7.716262405861235</v>
+        <v>7.585275892952789</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9713393319329692</v>
+        <v>0.9706506876082238</v>
       </c>
     </row>
     <row r="16">
@@ -1025,19 +1025,19 @@
         <v>985.0107317824941</v>
       </c>
       <c r="G16" t="n">
-        <v>3.747264497291497</v>
+        <v>3.747264497291508</v>
       </c>
       <c r="H16" t="n">
-        <v>5.067471482717012</v>
+        <v>5.067471482717011</v>
       </c>
       <c r="I16" t="n">
-        <v>90.39985645846278</v>
+        <v>90.39985262243552</v>
       </c>
       <c r="J16" t="n">
-        <v>6.308978039494022</v>
+        <v>6.148057097071797</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9670536087390886</v>
+        <v>0.965184526666955</v>
       </c>
     </row>
     <row r="17">
@@ -1062,19 +1062,19 @@
         <v>992.2539094228936</v>
       </c>
       <c r="G17" t="n">
-        <v>3.796557778379082</v>
+        <v>3.796557778379044</v>
       </c>
       <c r="H17" t="n">
-        <v>5.426218107233474</v>
+        <v>5.42621810723347</v>
       </c>
       <c r="I17" t="n">
-        <v>90.0675843031344</v>
+        <v>90.06757441015667</v>
       </c>
       <c r="J17" t="n">
-        <v>6.796441376870342</v>
+        <v>6.647340254345798</v>
       </c>
       <c r="K17" t="n">
-        <v>0.9644590495966724</v>
+        <v>0.9629997598938843</v>
       </c>
     </row>
     <row r="18">
@@ -1087,31 +1087,31 @@
         <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.9823306052616613</v>
+        <v>-0.9769674601801612</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9150562646187159</v>
+        <v>1.316069276597882</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9289872559292436</v>
+        <v>1.135957426920155</v>
       </c>
       <c r="F18" t="n">
-        <v>929.4248881644673</v>
+        <v>876.4872436174745</v>
       </c>
       <c r="G18" t="n">
-        <v>2.699120004101129</v>
+        <v>3.156527371826327</v>
       </c>
       <c r="H18" t="n">
-        <v>4.668149422396129</v>
+        <v>5.702982121395989</v>
       </c>
       <c r="I18" t="n">
-        <v>90.5607541698636</v>
+        <v>89.74993664942699</v>
       </c>
       <c r="J18" t="n">
-        <v>5.922758445777547</v>
+        <v>7.141809198787176</v>
       </c>
       <c r="K18" t="n">
-        <v>0.9639050007391152</v>
+        <v>0.9618202116985695</v>
       </c>
     </row>
     <row r="19">
@@ -1124,31 +1124,31 @@
         <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.9769674601801612</v>
+        <v>-0.9823306052616613</v>
       </c>
       <c r="D19" t="n">
-        <v>1.316069276597882</v>
+        <v>0.9150562646187159</v>
       </c>
       <c r="E19" t="n">
-        <v>1.135957426920155</v>
+        <v>0.9289872559292436</v>
       </c>
       <c r="F19" t="n">
-        <v>876.4872436174745</v>
+        <v>929.4248881644673</v>
       </c>
       <c r="G19" t="n">
-        <v>3.156527371826424</v>
+        <v>2.699120004101111</v>
       </c>
       <c r="H19" t="n">
-        <v>5.702982121395996</v>
+        <v>4.668149422396124</v>
       </c>
       <c r="I19" t="n">
-        <v>89.74995231163449</v>
+        <v>90.56077671501814</v>
       </c>
       <c r="J19" t="n">
-        <v>7.280783709884942</v>
+        <v>5.751021662752048</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9629045430792834</v>
+        <v>0.9616198324114469</v>
       </c>
     </row>
     <row r="20">
@@ -1173,19 +1173,19 @@
         <v>898.2723991317932</v>
       </c>
       <c r="G20" t="n">
-        <v>3.28903516376212</v>
+        <v>3.28903516376206</v>
       </c>
       <c r="H20" t="n">
-        <v>5.776915649715219</v>
+        <v>5.776915649715216</v>
       </c>
       <c r="I20" t="n">
-        <v>89.6833801685386</v>
+        <v>89.68336320014809</v>
       </c>
       <c r="J20" t="n">
-        <v>7.357544752720455</v>
+        <v>7.220049508710101</v>
       </c>
       <c r="K20" t="n">
-        <v>0.9618671557218104</v>
+        <v>0.9608314970186986</v>
       </c>
     </row>
     <row r="21">
@@ -1210,19 +1210,19 @@
         <v>515.0249161515285</v>
       </c>
       <c r="G21" t="n">
-        <v>3.870251075537623</v>
+        <v>3.870251075537601</v>
       </c>
       <c r="H21" t="n">
-        <v>6.926465120882433</v>
+        <v>6.926465120882428</v>
       </c>
       <c r="I21" t="n">
-        <v>88.53820866387127</v>
+        <v>88.53822308039622</v>
       </c>
       <c r="J21" t="n">
-        <v>9.148951676895154</v>
+        <v>9.038740763193681</v>
       </c>
       <c r="K21" t="n">
-        <v>0.9598366011229844</v>
+        <v>0.959929588314794</v>
       </c>
     </row>
     <row r="22">
@@ -1247,19 +1247,19 @@
         <v>959.2222212006562</v>
       </c>
       <c r="G22" t="n">
-        <v>3.054853077716411</v>
+        <v>3.054853077716398</v>
       </c>
       <c r="H22" t="n">
         <v>4.911296439845443</v>
       </c>
       <c r="I22" t="n">
-        <v>90.6398084036133</v>
+        <v>90.63981244359209</v>
       </c>
       <c r="J22" t="n">
-        <v>6.124067204543739</v>
+        <v>5.958147515790889</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9022141473246829</v>
+        <v>0.8997544932169158</v>
       </c>
     </row>
     <row r="23">
@@ -1284,19 +1284,19 @@
         <v>934.4784837879893</v>
       </c>
       <c r="G23" t="n">
-        <v>2.796265769646185</v>
+        <v>2.796265769646167</v>
       </c>
       <c r="H23" t="n">
-        <v>5.842139841967368</v>
+        <v>5.842139841967365</v>
       </c>
       <c r="I23" t="n">
-        <v>89.75866628974364</v>
+        <v>89.75865251071539</v>
       </c>
       <c r="J23" t="n">
-        <v>7.659917675053562</v>
+        <v>7.527948010341123</v>
       </c>
       <c r="K23" t="n">
-        <v>0.8984333812819097</v>
+        <v>0.8974943145771177</v>
       </c>
     </row>
     <row r="24">
@@ -1321,19 +1321,19 @@
         <v>929.8717425622768</v>
       </c>
       <c r="G24" t="n">
-        <v>2.829558566575855</v>
+        <v>2.829558566575798</v>
       </c>
       <c r="H24" t="n">
-        <v>5.897459292430044</v>
+        <v>5.897459292430039</v>
       </c>
       <c r="I24" t="n">
-        <v>89.76512460309408</v>
+        <v>89.76510962162777</v>
       </c>
       <c r="J24" t="n">
-        <v>7.645550143864765</v>
+        <v>7.513329003516862</v>
       </c>
       <c r="K24" t="n">
-        <v>0.8978683788860985</v>
+        <v>0.8969159195877332</v>
       </c>
     </row>
     <row r="25">
@@ -1358,19 +1358,19 @@
         <v>933.5863365500767</v>
       </c>
       <c r="G25" t="n">
-        <v>3.20622426965001</v>
+        <v>3.206224269650008</v>
       </c>
       <c r="H25" t="n">
-        <v>5.873811846390026</v>
+        <v>5.873811846390021</v>
       </c>
       <c r="I25" t="n">
-        <v>89.65561914260337</v>
+        <v>89.65560004584962</v>
       </c>
       <c r="J25" t="n">
-        <v>7.716262405861235</v>
+        <v>7.585275892952789</v>
       </c>
       <c r="K25" t="n">
-        <v>0.8943638495826465</v>
+        <v>0.8934305381817269</v>
       </c>
     </row>
     <row r="26">
@@ -1395,19 +1395,19 @@
         <v>985.0107317824941</v>
       </c>
       <c r="G26" t="n">
-        <v>3.747264497291497</v>
+        <v>3.747264497291508</v>
       </c>
       <c r="H26" t="n">
-        <v>5.067471482717012</v>
+        <v>5.067471482717011</v>
       </c>
       <c r="I26" t="n">
-        <v>90.39985645846278</v>
+        <v>90.39985262243552</v>
       </c>
       <c r="J26" t="n">
-        <v>6.308978039494022</v>
+        <v>6.148057097071797</v>
       </c>
       <c r="K26" t="n">
-        <v>0.8931426912799526</v>
+        <v>0.8907958903614385</v>
       </c>
     </row>
     <row r="27">
@@ -1432,19 +1432,19 @@
         <v>929.4248881644673</v>
       </c>
       <c r="G27" t="n">
-        <v>2.699120004101129</v>
+        <v>2.699120004101111</v>
       </c>
       <c r="H27" t="n">
-        <v>4.668149422396129</v>
+        <v>4.668149422396124</v>
       </c>
       <c r="I27" t="n">
-        <v>90.5607541698636</v>
+        <v>90.56077671501814</v>
       </c>
       <c r="J27" t="n">
-        <v>5.922758445777547</v>
+        <v>5.751021662752048</v>
       </c>
       <c r="K27" t="n">
-        <v>0.8919703869400633</v>
+        <v>0.8891257011437029</v>
       </c>
     </row>
     <row r="28">
@@ -1469,19 +1469,19 @@
         <v>992.2539094228936</v>
       </c>
       <c r="G28" t="n">
-        <v>3.796557778379082</v>
+        <v>3.796557778379044</v>
       </c>
       <c r="H28" t="n">
-        <v>5.426218107233474</v>
+        <v>5.42621810723347</v>
       </c>
       <c r="I28" t="n">
-        <v>90.0675843031344</v>
+        <v>90.06757441015667</v>
       </c>
       <c r="J28" t="n">
-        <v>6.796441376870342</v>
+        <v>6.647340254345798</v>
       </c>
       <c r="K28" t="n">
-        <v>0.8883538651960253</v>
+        <v>0.8864947352731956</v>
       </c>
     </row>
     <row r="29">
@@ -1494,31 +1494,31 @@
         <v>8</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.9779437557508321</v>
+        <v>-0.9769674601801612</v>
       </c>
       <c r="D29" t="n">
-        <v>1.137208374331435</v>
+        <v>1.316069276597882</v>
       </c>
       <c r="E29" t="n">
-        <v>1.034730357262841</v>
+        <v>1.135957426920155</v>
       </c>
       <c r="F29" t="n">
-        <v>931.7453413415755</v>
+        <v>876.4872436174745</v>
       </c>
       <c r="G29" t="n">
-        <v>2.840062785113513</v>
+        <v>3.156527371826327</v>
       </c>
       <c r="H29" t="n">
-        <v>3.747907256253344</v>
+        <v>5.702982121395989</v>
       </c>
       <c r="I29" t="n">
-        <v>91.1673747434628</v>
+        <v>89.74993664942699</v>
       </c>
       <c r="J29" t="n">
-        <v>4.50137399483912</v>
+        <v>7.141809198787176</v>
       </c>
       <c r="K29" t="n">
-        <v>0.8862702536174148</v>
+        <v>0.8839836189077072</v>
       </c>
     </row>
     <row r="30">
@@ -1531,31 +1531,31 @@
         <v>9</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.9769674601801612</v>
+        <v>-0.9721285817721056</v>
       </c>
       <c r="D30" t="n">
-        <v>1.316069276597882</v>
+        <v>1.409497651804372</v>
       </c>
       <c r="E30" t="n">
-        <v>1.135957426920155</v>
+        <v>1.139020468446611</v>
       </c>
       <c r="F30" t="n">
-        <v>876.4872436174745</v>
+        <v>898.2723991317932</v>
       </c>
       <c r="G30" t="n">
-        <v>3.156527371826424</v>
+        <v>3.28903516376206</v>
       </c>
       <c r="H30" t="n">
-        <v>5.702982121395996</v>
+        <v>5.776915649715216</v>
       </c>
       <c r="I30" t="n">
-        <v>89.74995231163449</v>
+        <v>89.68336320014809</v>
       </c>
       <c r="J30" t="n">
-        <v>7.280783709884942</v>
+        <v>7.220049508710101</v>
       </c>
       <c r="K30" t="n">
-        <v>0.8853951048478177</v>
+        <v>0.8824626865714968</v>
       </c>
     </row>
     <row r="31">
@@ -1568,31 +1568,31 @@
         <v>10</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.9811933193599203</v>
+        <v>-0.9779437557508321</v>
       </c>
       <c r="D31" t="n">
-        <v>1.22762208371563</v>
+        <v>1.137208374331435</v>
       </c>
       <c r="E31" t="n">
-        <v>1.064502946919722</v>
+        <v>1.034730357262841</v>
       </c>
       <c r="F31" t="n">
-        <v>924.5040419813747</v>
+        <v>931.7453413415755</v>
       </c>
       <c r="G31" t="n">
-        <v>3.163171815034923</v>
+        <v>2.840062785113556</v>
       </c>
       <c r="H31" t="n">
-        <v>4.205589412116763</v>
+        <v>3.747907256253351</v>
       </c>
       <c r="I31" t="n">
-        <v>90.89747562682783</v>
+        <v>91.16739659197755</v>
       </c>
       <c r="J31" t="n">
-        <v>5.053048234033386</v>
+        <v>4.272865793738961</v>
       </c>
       <c r="K31" t="n">
-        <v>0.8850933818663099</v>
+        <v>0.881111455291364</v>
       </c>
     </row>
     <row r="32">
@@ -1617,16 +1617,16 @@
         <v>949.9437672416811</v>
       </c>
       <c r="G32" t="n">
-        <v>3.573205534136903</v>
+        <v>3.573205534136884</v>
       </c>
       <c r="H32" t="n">
-        <v>3.24368759667619</v>
+        <v>3.243687596676201</v>
       </c>
       <c r="I32" t="n">
-        <v>91.30996707586108</v>
+        <v>91.30998787304483</v>
       </c>
       <c r="J32" t="n">
-        <v>3.920672543020995</v>
+        <v>3.656040175436067</v>
       </c>
       <c r="K32" t="n">
         <v>1</v>
@@ -1654,19 +1654,19 @@
         <v>942.7992007445628</v>
       </c>
       <c r="G33" t="n">
-        <v>3.531804850656147</v>
+        <v>3.53180485065611</v>
       </c>
       <c r="H33" t="n">
-        <v>3.32172504499727</v>
+        <v>3.321725044997264</v>
       </c>
       <c r="I33" t="n">
-        <v>91.25089630595885</v>
+        <v>91.25091534501938</v>
       </c>
       <c r="J33" t="n">
-        <v>3.914372893174761</v>
+        <v>3.649285769746244</v>
       </c>
       <c r="K33" t="n">
-        <v>0.9987214814508965</v>
+        <v>0.9987214442433243</v>
       </c>
     </row>
     <row r="34">
@@ -1691,19 +1691,19 @@
         <v>934.9046332627136</v>
       </c>
       <c r="G34" t="n">
-        <v>3.62655535737608</v>
+        <v>3.626555357376058</v>
       </c>
       <c r="H34" t="n">
-        <v>3.200454623457622</v>
+        <v>3.200454623457623</v>
       </c>
       <c r="I34" t="n">
-        <v>91.17758522608594</v>
+        <v>91.17760507669671</v>
       </c>
       <c r="J34" t="n">
-        <v>3.689141740073292</v>
+        <v>3.406570131950328</v>
       </c>
       <c r="K34" t="n">
-        <v>0.997134747849363</v>
+        <v>0.9971347292554876</v>
       </c>
     </row>
     <row r="35">
@@ -1728,19 +1728,19 @@
         <v>931.7453413415755</v>
       </c>
       <c r="G35" t="n">
-        <v>2.840062785113513</v>
+        <v>2.840062785113556</v>
       </c>
       <c r="H35" t="n">
-        <v>3.747907256253344</v>
+        <v>3.747907256253351</v>
       </c>
       <c r="I35" t="n">
-        <v>91.1673747434628</v>
+        <v>91.16739659197755</v>
       </c>
       <c r="J35" t="n">
-        <v>4.50137399483912</v>
+        <v>4.272865793738961</v>
       </c>
       <c r="K35" t="n">
-        <v>0.9969137537527805</v>
+        <v>0.9969137785472499</v>
       </c>
     </row>
     <row r="36">
@@ -1765,19 +1765,19 @@
         <v>920.6093602048708</v>
       </c>
       <c r="G36" t="n">
-        <v>3.327401838298085</v>
+        <v>3.327401838298071</v>
       </c>
       <c r="H36" t="n">
-        <v>3.320354340229814</v>
+        <v>3.320354340229819</v>
       </c>
       <c r="I36" t="n">
-        <v>91.14406381519444</v>
+        <v>91.14408435230374</v>
       </c>
       <c r="J36" t="n">
-        <v>3.785907093209289</v>
+        <v>3.511132615275669</v>
       </c>
       <c r="K36" t="n">
-        <v>0.9964092156498024</v>
+        <v>0.9964092123938747</v>
       </c>
     </row>
     <row r="37">
@@ -1802,19 +1802,19 @@
         <v>925.5002716018744</v>
       </c>
       <c r="G37" t="n">
-        <v>3.382799933459086</v>
+        <v>3.382799933459056</v>
       </c>
       <c r="H37" t="n">
-        <v>3.365023341087159</v>
+        <v>3.365023341087163</v>
       </c>
       <c r="I37" t="n">
-        <v>91.14117216533427</v>
+        <v>91.14119354099101</v>
       </c>
       <c r="J37" t="n">
-        <v>3.830816977364589</v>
+        <v>3.559511431074056</v>
       </c>
       <c r="K37" t="n">
-        <v>0.9963466292303286</v>
+        <v>0.9963466441651414</v>
       </c>
     </row>
     <row r="38">
@@ -1839,19 +1839,19 @@
         <v>923.0590739530411</v>
       </c>
       <c r="G38" t="n">
-        <v>3.924471904352818</v>
+        <v>3.924471904352816</v>
       </c>
       <c r="H38" t="n">
-        <v>3.085105612326315</v>
+        <v>3.085105612326331</v>
       </c>
       <c r="I38" t="n">
-        <v>91.12413533741785</v>
+        <v>91.12415282241918</v>
       </c>
       <c r="J38" t="n">
-        <v>3.596123842908532</v>
+        <v>3.305609988145741</v>
       </c>
       <c r="K38" t="n">
-        <v>0.9959778867787731</v>
+        <v>0.995977817748596</v>
       </c>
     </row>
     <row r="39">
@@ -1876,19 +1876,19 @@
         <v>914.1938250082466</v>
       </c>
       <c r="G39" t="n">
-        <v>3.868361153298407</v>
+        <v>3.86836115329842</v>
       </c>
       <c r="H39" t="n">
-        <v>3.088727800196385</v>
+        <v>3.088727800196396</v>
       </c>
       <c r="I39" t="n">
-        <v>91.10251416084103</v>
+        <v>91.10253130777821</v>
       </c>
       <c r="J39" t="n">
-        <v>3.601730588151838</v>
+        <v>3.311708757138403</v>
       </c>
       <c r="K39" t="n">
-        <v>0.9955099213983883</v>
+        <v>0.9955098453604776</v>
       </c>
     </row>
     <row r="40">
@@ -1913,19 +1913,19 @@
         <v>995.3081445513959</v>
       </c>
       <c r="G40" t="n">
-        <v>4.455188922054814</v>
+        <v>4.455188922054784</v>
       </c>
       <c r="H40" t="n">
-        <v>3.239088734009982</v>
+        <v>3.239088734009979</v>
       </c>
       <c r="I40" t="n">
-        <v>91.09920572848431</v>
+        <v>91.09922138178663</v>
       </c>
       <c r="J40" t="n">
-        <v>3.816319291577537</v>
+        <v>3.543907253038084</v>
       </c>
       <c r="K40" t="n">
-        <v>0.9954383142034335</v>
+        <v>0.9954382058848678</v>
       </c>
     </row>
     <row r="41">
@@ -1950,19 +1950,19 @@
         <v>931.8309344717032</v>
       </c>
       <c r="G41" t="n">
-        <v>4.019868486109824</v>
+        <v>4.019868486109779</v>
       </c>
       <c r="H41" t="n">
-        <v>3.203065864940929</v>
+        <v>3.203065864940934</v>
       </c>
       <c r="I41" t="n">
-        <v>91.09526108828155</v>
+        <v>91.09527803674357</v>
       </c>
       <c r="J41" t="n">
-        <v>3.730931241987031</v>
+        <v>3.451784537733086</v>
       </c>
       <c r="K41" t="n">
-        <v>0.995352937024888</v>
+        <v>0.9953528567949624</v>
       </c>
     </row>
     <row r="42">
@@ -1989,10 +1989,10 @@
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="n">
-        <v>91.74258967979463</v>
+        <v>91.7425896797956</v>
       </c>
       <c r="J42" t="n">
-        <v>9.009802198610462</v>
+        <v>9.009802198609554</v>
       </c>
       <c r="K42" t="n">
         <v>1</v>
@@ -2022,13 +2022,13 @@
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="n">
-        <v>90.06981602005068</v>
+        <v>90.06981602005173</v>
       </c>
       <c r="J43" t="n">
-        <v>9.85485793246372</v>
+        <v>9.854857932462682</v>
       </c>
       <c r="K43" t="n">
-        <v>0.9104318996847025</v>
+        <v>0.9104318996846936</v>
       </c>
     </row>
     <row r="44">
@@ -2055,13 +2055,13 @@
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="n">
-        <v>90.24520500321567</v>
+        <v>90.24520500321636</v>
       </c>
       <c r="J44" t="n">
-        <v>9.160204551784455</v>
+        <v>9.160204551783549</v>
       </c>
       <c r="K44" t="n">
-        <v>0.8795250610348001</v>
+        <v>0.8795250610347716</v>
       </c>
     </row>
     <row r="45">
@@ -2088,13 +2088,13 @@
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="n">
-        <v>92.67172665235434</v>
+        <v>92.67172665235458</v>
       </c>
       <c r="J45" t="n">
-        <v>5.548446020966651</v>
+        <v>5.548446020966241</v>
       </c>
       <c r="K45" t="n">
-        <v>0.8730513374814041</v>
+        <v>0.87305133748138</v>
       </c>
     </row>
     <row r="46">
@@ -2121,13 +2121,13 @@
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="n">
-        <v>91.99861798254969</v>
+        <v>91.99861798255006</v>
       </c>
       <c r="J46" t="n">
-        <v>6.600198605183674</v>
+        <v>6.600198605183064</v>
       </c>
       <c r="K46" t="n">
-        <v>0.8698040845840262</v>
+        <v>0.8698040845839985</v>
       </c>
     </row>
     <row r="47">
@@ -2154,13 +2154,13 @@
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
-        <v>89.41980399291042</v>
+        <v>89.4198039929116</v>
       </c>
       <c r="J47" t="n">
-        <v>10.0175887838013</v>
+        <v>10.01758878380028</v>
       </c>
       <c r="K47" t="n">
-        <v>0.8696184009877788</v>
+        <v>0.8696184009877781</v>
       </c>
     </row>
     <row r="48">
@@ -2187,13 +2187,13 @@
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
-        <v>89.53083789477527</v>
+        <v>89.53083789477625</v>
       </c>
       <c r="J48" t="n">
-        <v>9.877889721312737</v>
+        <v>9.877889721311668</v>
       </c>
       <c r="K48" t="n">
-        <v>0.869160662628951</v>
+        <v>0.8691606626289327</v>
       </c>
     </row>
     <row r="49">
@@ -2220,13 +2220,13 @@
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
-        <v>89.54406129959926</v>
+        <v>89.5440612996003</v>
       </c>
       <c r="J49" t="n">
-        <v>9.860568490834067</v>
+        <v>9.860568490832996</v>
       </c>
       <c r="K49" t="n">
-        <v>0.8690656606071049</v>
+        <v>0.869065660607091</v>
       </c>
     </row>
     <row r="50">
@@ -2253,13 +2253,13 @@
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="n">
-        <v>90.77406497324741</v>
+        <v>90.77406497324782</v>
       </c>
       <c r="J50" t="n">
-        <v>8.263901657915735</v>
+        <v>8.263901657914843</v>
       </c>
       <c r="K50" t="n">
-        <v>0.8654975949588295</v>
+        <v>0.8654975949587819</v>
       </c>
     </row>
     <row r="51">
@@ -2286,13 +2286,13 @@
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="n">
-        <v>92.57526345946627</v>
+        <v>92.57526345946644</v>
       </c>
       <c r="J51" t="n">
-        <v>5.527255766739317</v>
+        <v>5.527255766738929</v>
       </c>
       <c r="K51" t="n">
-        <v>0.8614905611949827</v>
+        <v>0.8614905611949526</v>
       </c>
     </row>
   </sheetData>
